--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dosage-instructions.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dosage-instructions.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -319,7 +319,7 @@
 Exemple - 400µg pendant une minute (perfusion): {'numerator':{'value':400,'unit':'µg','system':'http://unitsofmeasure.org','code':'µg'},'denominator':{'value':1,'unit':'min','system':'http://unitsofmeasure.org','code':'min'}}</t>
   </si>
   <si>
-    <t>fr-lm-dosage-instructions.dosageDetails.dateDePrise</t>
+    <t>fr-lm-dosage-instructions.dosageDetails.dateOfAdministration</t>
   </si>
   <si>
     <t xml:space="preserve">dateTime
@@ -329,7 +329,7 @@
     <t>Date précise du moment de prise</t>
   </si>
   <si>
-    <t>fr-lm-dosage-instructions.dosageDetails.conditionDePrise</t>
+    <t>fr-lm-dosage-instructions.dosageDetails.conditionOfAdministration</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dosage-instructions.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dosage-instructions.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dosage-instructions.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dosage-instructions.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dosage-instructions.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dosage-instructions.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dosage-instructions.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dosage-instructions.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Posologie</t>
+    <t>Entrée Posologie</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dosage-instructions.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dosage-instructions.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dosage-instructions.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dosage-instructions.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dosage-instructions.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dosage-instructions.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
